--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2615-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2615-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E08AC474-7785-4B11-AEBB-C0B4788FEFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5ACF9831-BFA6-4C8F-9091-AC99AE647826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4892AF9C-9625-411B-814C-6B17AD237886}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B4810547-CE98-465E-841F-B243F3662B00}"/>
   </bookViews>
   <sheets>
     <sheet name="2615-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1577,27 +1577,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA9562D-BB17-47D0-947F-3494E5AE83F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23FE84C6-F471-4BCE-8C13-A90470B64F98}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1630,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1667,7 +1666,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1719,7 +1718,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1787,7 +1786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1859,7 +1858,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1931,7 +1930,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2363,7 +2362,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2507,7 +2506,7 @@
         <v>8.2200000000000006</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2579,7 +2578,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2651,7 +2650,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2723,7 +2722,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2795,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2867,7 +2866,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2939,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3011,7 +3010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="42">
         <v>2007</v>
       </c>
@@ -3083,7 +3082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
       <c r="B23" s="45"/>
       <c r="C23" s="18" t="s">
@@ -3111,7 +3110,7 @@
       <c r="W23" s="51"/>
       <c r="X23" s="47"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2006</v>
       </c>
@@ -3183,7 +3182,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2005</v>
       </c>
@@ -3255,7 +3254,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="44"/>
       <c r="B26" s="45"/>
       <c r="C26" s="18" t="s">
@@ -3283,7 +3282,7 @@
       <c r="W26" s="51"/>
       <c r="X26" s="47"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="52">
         <v>2004</v>
       </c>
@@ -3355,7 +3354,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="54"/>
       <c r="B28" s="55"/>
       <c r="C28" s="20" t="s">
@@ -3383,7 +3382,7 @@
       <c r="W28" s="61"/>
       <c r="X28" s="57"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2003</v>
       </c>
@@ -3455,7 +3454,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2002</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>9.92</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2001</v>
       </c>
@@ -3599,7 +3598,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="52">
         <v>2000</v>
       </c>
@@ -3671,7 +3670,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="54"/>
       <c r="B33" s="55"/>
       <c r="C33" s="20" t="s">
@@ -3699,7 +3698,7 @@
       <c r="W33" s="61"/>
       <c r="X33" s="57"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>1999</v>
       </c>
@@ -3771,7 +3770,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1998</v>
       </c>
@@ -3843,7 +3842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>1997</v>
       </c>
@@ -3915,7 +3914,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1996</v>
       </c>
@@ -3987,7 +3986,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <v>1995</v>
       </c>
@@ -4059,7 +4058,7 @@
         <v>8.0399999999999991</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1994</v>
       </c>
@@ -4131,7 +4130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>1993</v>
       </c>
@@ -4203,7 +4202,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1992</v>
       </c>
@@ -4275,7 +4274,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="40" t="s">
         <v>60</v>
       </c>
